--- a/packages/examples/showcase/deal-desk-quote-review/artifact/deal-desk-quote-review.xlsx
+++ b/packages/examples/showcase/deal-desk-quote-review/artifact/deal-desk-quote-review.xlsx
@@ -1838,7 +1838,7 @@
   </mergeCells>
   <conditionalFormatting sqref="O2:O25">
     <cfRule type="expression" dxfId="0" priority="1">
-      <formula>(M2&gt;=0.18)</formula>
+      <formula>($O2&lt;0.18)</formula>
     </cfRule>
     <cfRule type="expression" dxfId="1" priority="2">
       <formula>(M2&lt;0.08)</formula>

--- a/packages/examples/showcase/deal-desk-quote-review/artifact/deal-desk-quote-review.xlsx
+++ b/packages/examples/showcase/deal-desk-quote-review/artifact/deal-desk-quote-review.xlsx
@@ -5,6 +5,7 @@
     <sheet name="Quote Review" sheetId="1" r:id="rId1"/>
     <sheet name="Approvals" sheetId="2" r:id="rId2"/>
   </sheets>
+  <calcPr calcMode="auto" fullCalcOnLoad="1" forceFullCalc="1"/>
 </workbook>
 </file>
 
@@ -591,6 +592,24 @@
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1"/>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
     </row>
     <row r="2" ht="30" customHeight="1">
       <c r="A2" s="2" t="s">
@@ -1896,6 +1915,14 @@
       <c r="A1" s="1" t="s">
         <v>103</v>
       </c>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+      <c r="I1" s="1"/>
     </row>
     <row r="2" ht="30" customHeight="1">
       <c r="A2" s="13" t="s">
